--- a/dist/Октоберфест_тайминг_по_дням_2026-10-23_25.xlsx
+++ b/dist/Октоберфест_тайминг_по_дням_2026-10-23_25.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kakorolkova\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kakorolkova\Nextcloud\Проекты\Королькова\Октоберфест\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6737EE76-1E97-43C8-8039-87AC1EEC396D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5A0439C-AF36-411E-9490-6B87688250EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Мероприятия и локации" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="54">
   <si>
     <t>Октоберфест. Мероприятия, локации и время по дням</t>
   </si>
@@ -68,30 +68,10 @@
     <t>—</t>
   </si>
   <si>
-    <t>Цикл 20–25 минут. 11:00–14:00¹ — окно детских МК; старт отдельного занятия не задан.</t>
-  </si>
-  <si>
     <t>«Осенний гербарий»
 Открытки из сухоцветов</t>
   </si>
   <si>
-    <t>Цикл 15–20 минут. 11:00–14:00¹ — окно детских МК; старт отдельного занятия не задан.</t>
-  </si>
-  <si>
-    <t>«Музыкальная шкатулка»
-Шумовые инструменты</t>
-  </si>
-  <si>
-    <t>Цикл 20 минут. 11:00–14:00¹ — окно детских МК; старт отдельного занятия не задан.</t>
-  </si>
-  <si>
-    <t>«Пряничная подкова»
-Роспись пряников</t>
-  </si>
-  <si>
-    <t>Цикл 20 минут, до 10–12 детей одновременно. Старт отдельного занятия не задан.</t>
-  </si>
-  <si>
     <t>ИНТЕРАКТИВЫ В ПАРКЕ — площадки работают параллельно</t>
   </si>
   <si>
@@ -120,9 +100,6 @@
     <t>Бирпонг</t>
   </si>
   <si>
-    <t>Один из шатров «Нитро»*</t>
-  </si>
-  <si>
     <t>Место предложено как вариант: «в идеале один из шатров Нитро».</t>
   </si>
   <si>
@@ -191,12 +168,6 @@
     <t>Проведение условное: «если будет смысл в этом, то запустим». После закрытия фестиваля в 22:00.</t>
   </si>
   <si>
-    <t>* Детские МК: в строке 18 плана и приложении названа площадь перед сценой; в строках 4 и 11 плана осталось «уточняется».</t>
-  </si>
-  <si>
-    <t>* Бирпонг: в плане и программе локация сформулирована как вариант — «в идеале один из шатров Нитро».</t>
-  </si>
-  <si>
     <t>Плохая погода: ведущий — сцена Лофта; интерактивы — у Лофта либо внутри.</t>
   </si>
   <si>
@@ -213,6 +184,15 @@
   </si>
   <si>
     <t>В пятницу одна подача. В субботу и воскресенье 2 раза по два часа по сигналу ведущего.</t>
+  </si>
+  <si>
+    <t>Один из шатров «Нитро»</t>
+  </si>
+  <si>
+    <t>Цикл 20–25 минут. 11:00–14:00 — окно детских МК; старт отдельного занятия не задан.</t>
+  </si>
+  <si>
+    <t>Цикл 15–20 минут. 11:00–14:00 — окно детских МК; старт отдельного занятия не задан.</t>
   </si>
 </sst>
 </file>
@@ -376,14 +356,14 @@
     <xf numFmtId="167" fontId="1" fillId="4" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="164" fontId="3" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -619,7 +599,7 @@
   <sheetPr>
     <tabColor rgb="FF263F55"/>
   </sheetPr>
-  <dimension ref="A1:I35"/>
+  <dimension ref="A1:I31"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="37" customWidth="1"/>
@@ -692,35 +672,35 @@
     <row r="6" spans="1:9" ht="26" customHeight="1">
       <c r="A6" s="4"/>
       <c r="B6" s="4"/>
-      <c r="C6" s="14">
+      <c r="C6" s="15">
         <v>46318</v>
       </c>
-      <c r="D6" s="15"/>
-      <c r="E6" s="14">
+      <c r="D6" s="16"/>
+      <c r="E6" s="15">
         <v>46319</v>
       </c>
-      <c r="F6" s="15"/>
-      <c r="G6" s="14">
+      <c r="F6" s="16"/>
+      <c r="G6" s="15">
         <v>46320</v>
       </c>
-      <c r="H6" s="15"/>
+      <c r="H6" s="16"/>
       <c r="I6" s="4"/>
     </row>
     <row r="7" spans="1:9" ht="38" customHeight="1">
       <c r="A7" s="4"/>
       <c r="B7" s="4"/>
-      <c r="C7" s="15" t="s">
+      <c r="C7" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="D7" s="15"/>
-      <c r="E7" s="15" t="s">
+      <c r="D7" s="16"/>
+      <c r="E7" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="F7" s="15"/>
-      <c r="G7" s="15" t="s">
+      <c r="F7" s="16"/>
+      <c r="G7" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="H7" s="15"/>
+      <c r="H7" s="16"/>
       <c r="I7" s="4"/>
     </row>
     <row r="8" spans="1:9" ht="31" customHeight="1">
@@ -753,17 +733,17 @@
       </c>
     </row>
     <row r="9" spans="1:9" ht="31" customHeight="1">
-      <c r="A9" s="16" t="s">
-        <v>55</v>
-      </c>
-      <c r="B9" s="16"/>
-      <c r="C9" s="16"/>
-      <c r="D9" s="16"/>
-      <c r="E9" s="16"/>
-      <c r="F9" s="16"/>
-      <c r="G9" s="16"/>
-      <c r="H9" s="16"/>
-      <c r="I9" s="16"/>
+      <c r="A9" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="B9" s="14"/>
+      <c r="C9" s="14"/>
+      <c r="D9" s="14"/>
+      <c r="E9" s="14"/>
+      <c r="F9" s="14"/>
+      <c r="G9" s="14"/>
+      <c r="H9" s="14"/>
+      <c r="I9" s="14"/>
     </row>
     <row r="10" spans="1:9" ht="65" customHeight="1">
       <c r="A10" s="5" t="s">
@@ -791,12 +771,12 @@
         <v>0.58333333333333337</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>14</v>
+        <v>52</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="65" customHeight="1">
       <c r="A11" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>12</v>
@@ -820,86 +800,86 @@
         <v>0.58333333333333337</v>
       </c>
       <c r="I11" s="5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" ht="65" customHeight="1">
-      <c r="A12" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D12" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E12" s="11">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="F12" s="11">
-        <v>0.58333333333333337</v>
-      </c>
-      <c r="G12" s="12">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="H12" s="12">
-        <v>0.58333333333333337</v>
-      </c>
-      <c r="I12" s="5" t="s">
-        <v>18</v>
-      </c>
+        <v>53</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="31" customHeight="1">
+      <c r="A12" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12" s="14"/>
+      <c r="C12" s="14"/>
+      <c r="D12" s="14"/>
+      <c r="E12" s="14"/>
+      <c r="F12" s="14"/>
+      <c r="G12" s="14"/>
+      <c r="H12" s="14"/>
+      <c r="I12" s="14"/>
     </row>
     <row r="13" spans="1:9" ht="65" customHeight="1">
       <c r="A13" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C13" s="6">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="D13" s="6">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="E13" s="7">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="F13" s="7">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="G13" s="8">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="H13" s="8">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="I13" s="5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="65" customHeight="1">
+      <c r="A14" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="B13" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C13" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D13" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E13" s="11">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="F13" s="11">
-        <v>0.58333333333333337</v>
-      </c>
-      <c r="G13" s="12">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="H13" s="12">
-        <v>0.58333333333333337</v>
-      </c>
-      <c r="I13" s="5" t="s">
+      <c r="B14" s="5" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="14" spans="1:9" ht="31" customHeight="1">
-      <c r="A14" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="B14" s="16"/>
-      <c r="C14" s="16"/>
-      <c r="D14" s="16"/>
-      <c r="E14" s="16"/>
-      <c r="F14" s="16"/>
-      <c r="G14" s="16"/>
-      <c r="H14" s="16"/>
-      <c r="I14" s="16"/>
+      <c r="C14" s="6">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="D14" s="6">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="E14" s="7">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="F14" s="7">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="G14" s="8">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="H14" s="8">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="I14" s="5" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="15" spans="1:9" ht="65" customHeight="1">
       <c r="A15" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B15" s="5" t="s">
         <v>22</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>23</v>
       </c>
       <c r="C15" s="6">
         <v>0.66666666666666663</v>
@@ -920,15 +900,15 @@
         <v>0.79166666666666663</v>
       </c>
       <c r="I15" s="5" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="65" customHeight="1">
       <c r="A16" s="5" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>26</v>
+        <v>51</v>
       </c>
       <c r="C16" s="6">
         <v>0.66666666666666663</v>
@@ -952,83 +932,83 @@
         <v>24</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="65" customHeight="1">
-      <c r="A17" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="C17" s="6">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="D17" s="6">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="E17" s="7">
-        <v>0.58333333333333337</v>
-      </c>
-      <c r="F17" s="7">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="G17" s="8">
-        <v>0.58333333333333337</v>
-      </c>
-      <c r="H17" s="8">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="I17" s="5" t="s">
-        <v>24</v>
-      </c>
+    <row r="17" spans="1:9" ht="31" customHeight="1">
+      <c r="A17" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="B17" s="14"/>
+      <c r="C17" s="14"/>
+      <c r="D17" s="14"/>
+      <c r="E17" s="14"/>
+      <c r="F17" s="14"/>
+      <c r="G17" s="14"/>
+      <c r="H17" s="14"/>
+      <c r="I17" s="14"/>
     </row>
     <row r="18" spans="1:9" ht="65" customHeight="1">
       <c r="A18" s="5" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="C18" s="6">
+        <v>26</v>
+      </c>
+      <c r="C18" s="13">
         <v>0.66666666666666663</v>
       </c>
-      <c r="D18" s="6">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="E18" s="7">
-        <v>0.58333333333333337</v>
-      </c>
-      <c r="F18" s="7">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="G18" s="8">
-        <v>0.58333333333333337</v>
-      </c>
-      <c r="H18" s="8">
-        <v>0.79166666666666663</v>
+      <c r="D18" s="13">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="E18" s="11">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="F18" s="11">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="G18" s="12">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="H18" s="12">
+        <v>0.75</v>
       </c>
       <c r="I18" s="5" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" ht="31" customHeight="1">
-      <c r="A19" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="B19" s="16"/>
-      <c r="C19" s="16"/>
-      <c r="D19" s="16"/>
-      <c r="E19" s="16"/>
-      <c r="F19" s="16"/>
-      <c r="G19" s="16"/>
-      <c r="H19" s="16"/>
-      <c r="I19" s="16"/>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="65" customHeight="1">
+      <c r="A19" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C19" s="13">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="D19" s="13">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="E19" s="11">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="F19" s="11">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="G19" s="12">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="H19" s="12">
+        <v>0.75</v>
+      </c>
+      <c r="I19" s="5" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="20" spans="1:9" ht="65" customHeight="1">
       <c r="A20" s="5" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C20" s="13">
         <v>0.66666666666666663</v>
@@ -1040,7 +1020,7 @@
         <v>0.58333333333333337</v>
       </c>
       <c r="F20" s="11">
-        <v>0.75</v>
+        <v>0.79166666666666663</v>
       </c>
       <c r="G20" s="12">
         <v>0.58333333333333337</v>
@@ -1049,15 +1029,15 @@
         <v>0.75</v>
       </c>
       <c r="I20" s="5" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="65" customHeight="1">
       <c r="A21" s="5" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C21" s="13">
         <v>0.66666666666666663</v>
@@ -1069,7 +1049,7 @@
         <v>0.58333333333333337</v>
       </c>
       <c r="F21" s="11">
-        <v>0.75</v>
+        <v>0.79166666666666663</v>
       </c>
       <c r="G21" s="12">
         <v>0.58333333333333337</v>
@@ -1078,186 +1058,186 @@
         <v>0.75</v>
       </c>
       <c r="I21" s="5" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" ht="65" customHeight="1">
-      <c r="A22" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="B22" s="5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" ht="31" customHeight="1">
+      <c r="A22" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="C22" s="13">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="D22" s="13">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="E22" s="11">
-        <v>0.58333333333333337</v>
-      </c>
-      <c r="F22" s="11">
-        <v>0.75</v>
-      </c>
-      <c r="G22" s="12">
-        <v>0.58333333333333337</v>
-      </c>
-      <c r="H22" s="12">
-        <v>0.75</v>
-      </c>
-      <c r="I22" s="5" t="s">
-        <v>37</v>
-      </c>
+      <c r="B22" s="14"/>
+      <c r="C22" s="14"/>
+      <c r="D22" s="14"/>
+      <c r="E22" s="14"/>
+      <c r="F22" s="14"/>
+      <c r="G22" s="14"/>
+      <c r="H22" s="14"/>
+      <c r="I22" s="14"/>
     </row>
     <row r="23" spans="1:9" ht="65" customHeight="1">
       <c r="A23" s="5" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="C23" s="13">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="D23" s="13">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="E23" s="11">
-        <v>0.58333333333333337</v>
-      </c>
-      <c r="F23" s="11">
+        <v>26</v>
+      </c>
+      <c r="C23" s="6">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="D23" s="6">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="E23" s="7">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="F23" s="7">
+        <v>0.625</v>
+      </c>
+      <c r="G23" s="8">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="H23" s="8">
+        <v>0.625</v>
+      </c>
+      <c r="I23" s="5" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" ht="65" customHeight="1">
+      <c r="A24" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E24" s="7">
         <v>0.75</v>
       </c>
-      <c r="G23" s="12">
-        <v>0.58333333333333337</v>
-      </c>
-      <c r="H23" s="12">
+      <c r="F24" s="7">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="G24" s="8">
         <v>0.75</v>
       </c>
-      <c r="I23" s="5" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" ht="31" customHeight="1">
-      <c r="A24" s="16" t="s">
-        <v>40</v>
-      </c>
-      <c r="B24" s="16"/>
-      <c r="C24" s="16"/>
-      <c r="D24" s="16"/>
-      <c r="E24" s="16"/>
-      <c r="F24" s="16"/>
-      <c r="G24" s="16"/>
-      <c r="H24" s="16"/>
-      <c r="I24" s="16"/>
+      <c r="H24" s="8">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="I24" s="5" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="25" spans="1:9" ht="65" customHeight="1">
       <c r="A25" s="5" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="C25" s="6">
-        <v>0.70833333333333337</v>
-      </c>
-      <c r="D25" s="6">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="E25" s="7">
-        <v>0.54166666666666663</v>
-      </c>
-      <c r="F25" s="7">
-        <v>0.625</v>
-      </c>
-      <c r="G25" s="8">
-        <v>0.54166666666666663</v>
-      </c>
-      <c r="H25" s="8">
-        <v>0.625</v>
+        <v>37</v>
+      </c>
+      <c r="C25" s="13">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="D25" s="13">
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="E25" s="11">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="F25" s="11">
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="G25" s="12">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="H25" s="12">
+        <v>0.91666666666666663</v>
       </c>
       <c r="I25" s="5" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" ht="65" customHeight="1">
-      <c r="A26" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="C26" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D26" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E26" s="7">
-        <v>0.75</v>
-      </c>
-      <c r="F26" s="7">
-        <v>0.83333333333333337</v>
-      </c>
-      <c r="G26" s="8">
-        <v>0.75</v>
-      </c>
-      <c r="H26" s="8">
-        <v>0.83333333333333337</v>
-      </c>
-      <c r="I26" s="5" t="s">
-        <v>59</v>
-      </c>
+        <v>38</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" ht="31" customHeight="1">
+      <c r="A26" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="B26" s="14"/>
+      <c r="C26" s="14"/>
+      <c r="D26" s="14"/>
+      <c r="E26" s="14"/>
+      <c r="F26" s="14"/>
+      <c r="G26" s="14"/>
+      <c r="H26" s="14"/>
+      <c r="I26" s="14"/>
     </row>
     <row r="27" spans="1:9" ht="65" customHeight="1">
       <c r="A27" s="5" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="C27" s="13">
+        <v>26</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D27" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E27" s="7">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="F27" s="7">
+        <v>0.875</v>
+      </c>
+      <c r="G27" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="H27" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="I27" s="5" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" ht="65" customHeight="1">
+      <c r="A28" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="C28" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E28" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F28" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G28" s="8">
         <v>0.66666666666666663</v>
       </c>
-      <c r="D27" s="13">
-        <v>0.91666666666666663</v>
-      </c>
-      <c r="E27" s="11">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="F27" s="11">
-        <v>0.91666666666666663</v>
-      </c>
-      <c r="G27" s="12">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="H27" s="12">
-        <v>0.91666666666666663</v>
-      </c>
-      <c r="I27" s="5" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" ht="31" customHeight="1">
-      <c r="A28" s="16" t="s">
-        <v>46</v>
-      </c>
-      <c r="B28" s="16"/>
-      <c r="C28" s="16"/>
-      <c r="D28" s="16"/>
-      <c r="E28" s="16"/>
-      <c r="F28" s="16"/>
-      <c r="G28" s="16"/>
-      <c r="H28" s="16"/>
-      <c r="I28" s="16"/>
+      <c r="H28" s="8">
+        <v>0.75</v>
+      </c>
+      <c r="I28" s="5" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="29" spans="1:9" ht="65" customHeight="1">
       <c r="A29" s="5" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="C29" s="6" t="s">
         <v>13</v>
@@ -1265,148 +1245,64 @@
       <c r="D29" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="E29" s="7">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="F29" s="7">
-        <v>0.875</v>
-      </c>
-      <c r="G29" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="H29" s="8" t="s">
-        <v>13</v>
+      <c r="E29" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F29" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G29" s="9">
+        <v>0.95833333333333337</v>
+      </c>
+      <c r="H29" s="10">
+        <v>4.1666666666666664E-2</v>
       </c>
       <c r="I29" s="5" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" ht="65" customHeight="1">
-      <c r="A30" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="C30" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D30" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E30" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F30" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="G30" s="8">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="H30" s="8">
-        <v>0.75</v>
-      </c>
-      <c r="I30" s="5" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" ht="65" customHeight="1">
-      <c r="A31" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="C31" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D31" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E31" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F31" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="G31" s="9">
-        <v>0.95833333333333337</v>
-      </c>
-      <c r="H31" s="10">
-        <v>4.1666666666666664E-2</v>
-      </c>
-      <c r="I31" s="5" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" ht="26" customHeight="1">
-      <c r="A32" s="1"/>
-      <c r="B32" s="1"/>
-      <c r="C32" s="1"/>
-      <c r="D32" s="1"/>
-      <c r="E32" s="1"/>
-      <c r="F32" s="1"/>
-      <c r="G32" s="1"/>
-      <c r="H32" s="1"/>
-      <c r="I32" s="1"/>
-    </row>
-    <row r="33" spans="1:9" ht="25" customHeight="1">
-      <c r="A33" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B33" s="1"/>
-      <c r="C33" s="1"/>
-      <c r="D33" s="1"/>
-      <c r="E33" s="1"/>
-      <c r="F33" s="1"/>
-      <c r="G33" s="1"/>
-      <c r="H33" s="1"/>
-      <c r="I33" s="1"/>
-    </row>
-    <row r="34" spans="1:9" ht="25" customHeight="1">
-      <c r="A34" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="B34" s="1"/>
-      <c r="C34" s="1"/>
-      <c r="D34" s="1"/>
-      <c r="E34" s="1"/>
-      <c r="F34" s="1"/>
-      <c r="G34" s="1"/>
-      <c r="H34" s="1"/>
-      <c r="I34" s="1"/>
-    </row>
-    <row r="35" spans="1:9" ht="25" customHeight="1">
-      <c r="A35" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="B35" s="1"/>
-      <c r="C35" s="1"/>
-      <c r="D35" s="1"/>
-      <c r="E35" s="1"/>
-      <c r="F35" s="1"/>
-      <c r="G35" s="1"/>
-      <c r="H35" s="1"/>
-      <c r="I35" s="1"/>
+        <v>44</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" ht="26" customHeight="1">
+      <c r="A30" s="1"/>
+      <c r="B30" s="1"/>
+      <c r="C30" s="1"/>
+      <c r="D30" s="1"/>
+      <c r="E30" s="1"/>
+      <c r="F30" s="1"/>
+      <c r="G30" s="1"/>
+      <c r="H30" s="1"/>
+      <c r="I30" s="1"/>
+    </row>
+    <row r="31" spans="1:9" ht="25" customHeight="1">
+      <c r="A31" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B31" s="1"/>
+      <c r="C31" s="1"/>
+      <c r="D31" s="1"/>
+      <c r="E31" s="1"/>
+      <c r="F31" s="1"/>
+      <c r="G31" s="1"/>
+      <c r="H31" s="1"/>
+      <c r="I31" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="A9:I9"/>
-    <mergeCell ref="A14:I14"/>
-    <mergeCell ref="A19:I19"/>
-    <mergeCell ref="A24:I24"/>
-    <mergeCell ref="A28:I28"/>
     <mergeCell ref="C6:D6"/>
     <mergeCell ref="C7:D7"/>
     <mergeCell ref="E6:F6"/>
     <mergeCell ref="E7:F7"/>
     <mergeCell ref="G6:H6"/>
     <mergeCell ref="G7:H7"/>
+    <mergeCell ref="A9:I9"/>
+    <mergeCell ref="A12:I12"/>
+    <mergeCell ref="A17:I17"/>
+    <mergeCell ref="A22:I22"/>
+    <mergeCell ref="A26:I26"/>
   </mergeCells>
-  <conditionalFormatting sqref="B10:B31">
+  <conditionalFormatting sqref="B10:B29">
     <cfRule type="containsText" dxfId="1" priority="2" operator="containsText" text="*"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C10:H31">
+  <conditionalFormatting sqref="C10:H29">
     <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="не задано"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/dist/Октоберфест_тайминг_по_дням_2026-10-23_25.xlsx
+++ b/dist/Октоберфест_тайминг_по_дням_2026-10-23_25.xlsx
@@ -8,27 +8,34 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kakorolkova\Nextcloud\Проекты\Королькова\Октоберфест\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5A0439C-AF36-411E-9490-6B87688250EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71A74382-0AB5-45A7-8D50-F1159AFF772E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Мероприятия и локации" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="42">
   <si>
     <t>Октоберфест. Мероприятия, локации и время по дням</t>
-  </si>
-  <si>
-    <t>Время московское. ¹ — границы общего блока, а не точное начало и окончание отдельного занятия или конкурса.</t>
-  </si>
-  <si>
-    <t>«—» — на этот день в тайминге не указано. Неуказанное время и спорные локации выделены жёлтым.</t>
   </si>
   <si>
     <t>Пятница
@@ -62,9 +69,6 @@
 Лепка из солёного теста</t>
   </si>
   <si>
-    <t>Площадь перед сценой*</t>
-  </si>
-  <si>
     <t>—</t>
   </si>
   <si>
@@ -78,53 +82,25 @@
     <t>Гонки с кружками</t>
   </si>
   <si>
-    <t>Аллея напротив Блинной</t>
-  </si>
-  <si>
-    <t>Станция работает параллельно с остальными интерактивами парка.</t>
-  </si>
-  <si>
     <t>Угадай сорт пива</t>
   </si>
   <si>
-    <t>Напротив цепочной карусели,
-у «Кофе Джой»</t>
-  </si>
-  <si>
     <t>Метание брецеля</t>
   </si>
   <si>
-    <t>Фуд-корт у верёвочного парка</t>
-  </si>
-  <si>
     <t>Бирпонг</t>
   </si>
   <si>
-    <t>Место предложено как вариант: «в идеале один из шатров Нитро».</t>
-  </si>
-  <si>
     <t>«Громовой удар»</t>
   </si>
   <si>
-    <t>Сцена</t>
-  </si>
-  <si>
-    <t>Блок ведущего¹: пт 16:00–19:00, сб–вс 14:00–18:00. В выходные — выходы по 30–45 мин каждый час. Старт конкурса не задан.</t>
-  </si>
-  <si>
     <t>«Держи кружку»</t>
   </si>
   <si>
     <t>Поедание сосисок</t>
   </si>
   <si>
-    <t>Конкурс — 2–3 минуты. Блок ведущего¹: пт 16:00–19:00, сб–вс 14:00–18:00. Точный старт конкурса не задан.</t>
-  </si>
-  <si>
     <t>Викторина по Октоберфесту</t>
-  </si>
-  <si>
-    <t>5–7 вопросов. Блок ведущего¹: пт 16:00–19:00, сб–вс 14:00–18:00. Длительность и старт викторины не заданы.</t>
   </si>
   <si>
     <t>ФУД — подача «Сказочной рульки» по сигналу ведущего</t>
@@ -141,13 +117,6 @@
     <t>Фудовый МК «Брецели»</t>
   </si>
   <si>
-    <t>Шатёр около Альпак;
-при плохой погоде — район Лофта</t>
-  </si>
-  <si>
-    <t>Указаны часы работы площадки¹. По плану МК проходят каждые 1,5–2 часа. Продолжительность одного занятия не указана.</t>
-  </si>
-  <si>
     <t>МУЗЫКА И ТРАНСЛЯЦИИ</t>
   </si>
   <si>
@@ -161,49 +130,53 @@
     <t>Лофт</t>
   </si>
   <si>
-    <t>Барселона — Реал Мадрид
-Возможная трансляция</t>
-  </si>
-  <si>
-    <t>Проведение условное: «если будет смысл в этом, то запустим». После закрытия фестиваля в 22:00.</t>
-  </si>
-  <si>
-    <t>Плохая погода: ведущий — сцена Лофта; интерактивы — у Лофта либо внутри.</t>
-  </si>
-  <si>
     <t xml:space="preserve">ДЕТСКИЕ МК </t>
   </si>
   <si>
     <t>КОНКУРСЫ ВЕДУЩЕГО — Точное время каждого конкурса не задано.</t>
   </si>
   <si>
-    <t>По таймингу программы: 16:00–18:00.</t>
-  </si>
-  <si>
-    <t>Суббота, 19:00–21:00 (2 часа).</t>
-  </si>
-  <si>
     <t>В пятницу одна подача. В субботу и воскресенье 2 раза по два часа по сигналу ведущего.</t>
   </si>
   <si>
-    <t>Один из шатров «Нитро»</t>
-  </si>
-  <si>
-    <t>Цикл 20–25 минут. 11:00–14:00 — окно детских МК; старт отдельного занятия не задан.</t>
-  </si>
-  <si>
-    <t>Цикл 15–20 минут. 11:00–14:00 — окно детских МК; старт отдельного занятия не задан.</t>
+    <t xml:space="preserve">Цикл 15–20 минут. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Цикл 20–25 минут. </t>
+  </si>
+  <si>
+    <t>фестивальный формат, участники сами подходят при желании</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> выходы ведущего 30–45 мин каждый час. </t>
+  </si>
+  <si>
+    <t>выходы ведущего 30–45 мин каждый час. Конкурс — 2–3 минуты</t>
+  </si>
+  <si>
+    <t>выходы ведущего 30–45 мин каждый час. 
+5–7 вопросов,связанных с историей фестиваля</t>
+  </si>
+  <si>
+    <t>у гриль станции (Гипнотик)</t>
+  </si>
+  <si>
+    <t>напротив Блинной</t>
+  </si>
+  <si>
+    <t>у Лофта</t>
+  </si>
+  <si>
+    <t>Указаны часы работы площадки. По плану МК проходят каждые 1,5–2 часа. Продолжительность одного занятия не указана.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="4">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="165" formatCode="hh:mm"/>
-    <numFmt numFmtId="166" formatCode="hh:mm&quot; ?&quot;"/>
-    <numFmt numFmtId="167" formatCode="hh:mm&quot;¹&quot;"/>
   </numFmts>
   <fonts count="6">
     <font>
@@ -246,7 +219,7 @@
       <name val="Carlito"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -276,11 +249,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFF6E7"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFE9BD"/>
       </patternFill>
     </fill>
   </fills>
@@ -315,7 +283,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -339,21 +307,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="1" fillId="6" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="1" fillId="7" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="1" fillId="7" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="1" fillId="5" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="1" fillId="6" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="1" fillId="4" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
@@ -598,8 +551,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <tabColor rgb="FF263F55"/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I31"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="37" customWidth="1"/>
@@ -633,145 +587,179 @@
       <c r="I2" s="1"/>
     </row>
     <row r="3" spans="1:9" ht="26" customHeight="1">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="4"/>
+      <c r="B3" s="4"/>
+      <c r="C3" s="10">
+        <v>46318</v>
+      </c>
+      <c r="D3" s="11"/>
+      <c r="E3" s="10">
+        <v>46319</v>
+      </c>
+      <c r="F3" s="11"/>
+      <c r="G3" s="10">
+        <v>46320</v>
+      </c>
+      <c r="H3" s="11"/>
+      <c r="I3" s="4"/>
+    </row>
+    <row r="4" spans="1:9" ht="38" customHeight="1">
+      <c r="A4" s="4"/>
+      <c r="B4" s="4"/>
+      <c r="C4" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
-      <c r="H3" s="1"/>
-      <c r="I3" s="1"/>
-    </row>
-    <row r="4" spans="1:9" ht="26" customHeight="1">
-      <c r="A4" s="1" t="s">
+      <c r="D4" s="11"/>
+      <c r="E4" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="1"/>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
-      <c r="H4" s="1"/>
-      <c r="I4" s="1"/>
-    </row>
-    <row r="5" spans="1:9" ht="26" customHeight="1">
-      <c r="A5" s="1"/>
-      <c r="B5" s="1"/>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
-      <c r="F5" s="1"/>
-      <c r="G5" s="1"/>
-      <c r="H5" s="1"/>
-      <c r="I5" s="1"/>
-    </row>
-    <row r="6" spans="1:9" ht="26" customHeight="1">
-      <c r="A6" s="4"/>
-      <c r="B6" s="4"/>
-      <c r="C6" s="15">
-        <v>46318</v>
-      </c>
-      <c r="D6" s="16"/>
-      <c r="E6" s="15">
-        <v>46319</v>
-      </c>
-      <c r="F6" s="16"/>
-      <c r="G6" s="15">
-        <v>46320</v>
-      </c>
-      <c r="H6" s="16"/>
-      <c r="I6" s="4"/>
-    </row>
-    <row r="7" spans="1:9" ht="38" customHeight="1">
-      <c r="A7" s="4"/>
-      <c r="B7" s="4"/>
-      <c r="C7" s="16" t="s">
+      <c r="F4" s="11"/>
+      <c r="G4" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="D7" s="16"/>
-      <c r="E7" s="16" t="s">
+      <c r="H4" s="11"/>
+      <c r="I4" s="4"/>
+    </row>
+    <row r="5" spans="1:9" ht="31" customHeight="1">
+      <c r="A5" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F7" s="16"/>
-      <c r="G7" s="16" t="s">
+      <c r="B5" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="H7" s="16"/>
-      <c r="I7" s="4"/>
-    </row>
-    <row r="8" spans="1:9" ht="31" customHeight="1">
-      <c r="A8" s="4" t="s">
+      <c r="C5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="D5" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="E5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I5" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D8" s="4" t="s">
+    </row>
+    <row r="6" spans="1:9" ht="31" customHeight="1">
+      <c r="A6" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="B6" s="9"/>
+      <c r="C6" s="9"/>
+      <c r="D6" s="9"/>
+      <c r="E6" s="9"/>
+      <c r="F6" s="9"/>
+      <c r="G6" s="9"/>
+      <c r="H6" s="9"/>
+      <c r="I6" s="9"/>
+    </row>
+    <row r="7" spans="1:9" ht="65" customHeight="1">
+      <c r="A7" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="E8" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="G8" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="H8" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="I8" s="4" t="s">
-        <v>10</v>
+      <c r="B7" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E7" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="F7" s="7">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="G7" s="8">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="H7" s="8">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="I7" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="65" customHeight="1">
+      <c r="A8" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E8" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="F8" s="7">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="G8" s="8">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="H8" s="8">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="I8" s="5" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="31" customHeight="1">
-      <c r="A9" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="B9" s="14"/>
-      <c r="C9" s="14"/>
-      <c r="D9" s="14"/>
-      <c r="E9" s="14"/>
-      <c r="F9" s="14"/>
-      <c r="G9" s="14"/>
-      <c r="H9" s="14"/>
-      <c r="I9" s="14"/>
+      <c r="A9" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" s="9"/>
+      <c r="C9" s="9"/>
+      <c r="D9" s="9"/>
+      <c r="E9" s="9"/>
+      <c r="F9" s="9"/>
+      <c r="G9" s="9"/>
+      <c r="H9" s="9"/>
+      <c r="I9" s="9"/>
     </row>
     <row r="10" spans="1:9" ht="65" customHeight="1">
       <c r="A10" s="5" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E10" s="11">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="F10" s="11">
-        <v>0.58333333333333337</v>
-      </c>
-      <c r="G10" s="12">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="H10" s="12">
-        <v>0.58333333333333337</v>
+        <v>38</v>
+      </c>
+      <c r="C10" s="6">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="D10" s="6">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="E10" s="7">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="F10" s="7">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="G10" s="8">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="H10" s="8">
+        <v>0.79166666666666663</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>52</v>
+        <v>34</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="65" customHeight="1">
@@ -779,49 +767,65 @@
         <v>14</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D11" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E11" s="11">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="F11" s="11">
-        <v>0.58333333333333337</v>
-      </c>
-      <c r="G11" s="12">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="H11" s="12">
-        <v>0.58333333333333337</v>
+        <v>28</v>
+      </c>
+      <c r="C11" s="6">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="D11" s="6">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="E11" s="7">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="F11" s="7">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="G11" s="8">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="H11" s="8">
+        <v>0.79166666666666663</v>
       </c>
       <c r="I11" s="5" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" ht="31" customHeight="1">
-      <c r="A12" s="14" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="65" customHeight="1">
+      <c r="A12" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B12" s="14"/>
-      <c r="C12" s="14"/>
-      <c r="D12" s="14"/>
-      <c r="E12" s="14"/>
-      <c r="F12" s="14"/>
-      <c r="G12" s="14"/>
-      <c r="H12" s="14"/>
-      <c r="I12" s="14"/>
+      <c r="B12" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="C12" s="6">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="D12" s="6">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="E12" s="7">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="F12" s="7">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="G12" s="8">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="H12" s="8">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="I12" s="5" t="s">
+        <v>34</v>
+      </c>
     </row>
     <row r="13" spans="1:9" ht="65" customHeight="1">
       <c r="A13" s="5" t="s">
         <v>16</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>17</v>
+        <v>40</v>
       </c>
       <c r="C13" s="6">
         <v>0.66666666666666663</v>
@@ -842,44 +846,28 @@
         <v>0.79166666666666663</v>
       </c>
       <c r="I13" s="5" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" ht="65" customHeight="1">
-      <c r="A14" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C14" s="6">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="D14" s="6">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="E14" s="7">
-        <v>0.58333333333333337</v>
-      </c>
-      <c r="F14" s="7">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="G14" s="8">
-        <v>0.58333333333333337</v>
-      </c>
-      <c r="H14" s="8">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="I14" s="5" t="s">
-        <v>18</v>
-      </c>
+        <v>34</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="31" customHeight="1">
+      <c r="A14" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="B14" s="9"/>
+      <c r="C14" s="9"/>
+      <c r="D14" s="9"/>
+      <c r="E14" s="9"/>
+      <c r="F14" s="9"/>
+      <c r="G14" s="9"/>
+      <c r="H14" s="9"/>
+      <c r="I14" s="9"/>
     </row>
     <row r="15" spans="1:9" ht="65" customHeight="1">
       <c r="A15" s="5" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="C15" s="6">
         <v>0.66666666666666663</v>
@@ -897,18 +885,18 @@
         <v>0.58333333333333337</v>
       </c>
       <c r="H15" s="8">
-        <v>0.79166666666666663</v>
+        <v>0.75</v>
       </c>
       <c r="I15" s="5" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="65" customHeight="1">
       <c r="A16" s="5" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>51</v>
+        <v>28</v>
       </c>
       <c r="C16" s="6">
         <v>0.66666666666666663</v>
@@ -926,385 +914,269 @@
         <v>0.58333333333333337</v>
       </c>
       <c r="H16" s="8">
-        <v>0.79166666666666663</v>
+        <v>0.75</v>
       </c>
       <c r="I16" s="5" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" ht="31" customHeight="1">
-      <c r="A17" s="14" t="s">
-        <v>47</v>
-      </c>
-      <c r="B17" s="14"/>
-      <c r="C17" s="14"/>
-      <c r="D17" s="14"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="14"/>
-      <c r="G17" s="14"/>
-      <c r="H17" s="14"/>
-      <c r="I17" s="14"/>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" ht="65" customHeight="1">
+      <c r="A17" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C17" s="6">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="D17" s="6">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="E17" s="7">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="F17" s="7">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="G17" s="8">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="H17" s="8">
+        <v>0.75</v>
+      </c>
+      <c r="I17" s="5" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="18" spans="1:9" ht="65" customHeight="1">
       <c r="A18" s="5" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="C18" s="13">
+        <v>28</v>
+      </c>
+      <c r="C18" s="6">
         <v>0.66666666666666663</v>
       </c>
-      <c r="D18" s="13">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="E18" s="11">
-        <v>0.58333333333333337</v>
-      </c>
-      <c r="F18" s="11">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="G18" s="12">
-        <v>0.58333333333333337</v>
-      </c>
-      <c r="H18" s="12">
+      <c r="D18" s="6">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="E18" s="7">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="F18" s="7">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="G18" s="8">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="H18" s="8">
         <v>0.75</v>
       </c>
       <c r="I18" s="5" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" ht="65" customHeight="1">
-      <c r="A19" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="C19" s="13">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="D19" s="13">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="E19" s="11">
-        <v>0.58333333333333337</v>
-      </c>
-      <c r="F19" s="11">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="G19" s="12">
-        <v>0.58333333333333337</v>
-      </c>
-      <c r="H19" s="12">
-        <v>0.75</v>
-      </c>
-      <c r="I19" s="5" t="s">
-        <v>27</v>
-      </c>
+        <v>37</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="31" customHeight="1">
+      <c r="A19" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="B19" s="9"/>
+      <c r="C19" s="9"/>
+      <c r="D19" s="9"/>
+      <c r="E19" s="9"/>
+      <c r="F19" s="9"/>
+      <c r="G19" s="9"/>
+      <c r="H19" s="9"/>
+      <c r="I19" s="9"/>
     </row>
     <row r="20" spans="1:9" ht="65" customHeight="1">
       <c r="A20" s="5" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="C20" s="13">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="D20" s="13">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="E20" s="11">
-        <v>0.58333333333333337</v>
-      </c>
-      <c r="F20" s="11">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="G20" s="12">
-        <v>0.58333333333333337</v>
-      </c>
-      <c r="H20" s="12">
-        <v>0.75</v>
+        <v>28</v>
+      </c>
+      <c r="C20" s="6">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="D20" s="6">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="E20" s="7">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="F20" s="7">
+        <v>0.625</v>
+      </c>
+      <c r="G20" s="8">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="H20" s="8">
+        <v>0.625</v>
       </c>
       <c r="I20" s="5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="65" customHeight="1">
       <c r="A21" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E21" s="7">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="F21" s="7">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="G21" s="8">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="H21" s="8">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="I21" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="B21" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="C21" s="13">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="D21" s="13">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="E21" s="11">
-        <v>0.58333333333333337</v>
-      </c>
-      <c r="F21" s="11">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="G21" s="12">
-        <v>0.58333333333333337</v>
-      </c>
-      <c r="H21" s="12">
-        <v>0.75</v>
-      </c>
-      <c r="I21" s="5" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" ht="31" customHeight="1">
-      <c r="A22" s="14" t="s">
-        <v>33</v>
-      </c>
-      <c r="B22" s="14"/>
-      <c r="C22" s="14"/>
-      <c r="D22" s="14"/>
-      <c r="E22" s="14"/>
-      <c r="F22" s="14"/>
-      <c r="G22" s="14"/>
-      <c r="H22" s="14"/>
-      <c r="I22" s="14"/>
-    </row>
-    <row r="23" spans="1:9" ht="65" customHeight="1">
-      <c r="A23" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="C23" s="6">
+    </row>
+    <row r="22" spans="1:9" ht="65" customHeight="1">
+      <c r="A22" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C22" s="6">
         <v>0.70833333333333337</v>
       </c>
-      <c r="D23" s="6">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="E23" s="7">
-        <v>0.54166666666666663</v>
-      </c>
-      <c r="F23" s="7">
-        <v>0.625</v>
-      </c>
-      <c r="G23" s="8">
-        <v>0.54166666666666663</v>
-      </c>
-      <c r="H23" s="8">
-        <v>0.625</v>
-      </c>
-      <c r="I23" s="5" t="s">
-        <v>50</v>
-      </c>
+      <c r="D22" s="6">
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="E22" s="7">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="F22" s="7">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="G22" s="8">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="H22" s="8">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="I22" s="5" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" ht="31" customHeight="1">
+      <c r="A23" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="B23" s="9"/>
+      <c r="C23" s="9"/>
+      <c r="D23" s="9"/>
+      <c r="E23" s="9"/>
+      <c r="F23" s="9"/>
+      <c r="G23" s="9"/>
+      <c r="H23" s="9"/>
+      <c r="I23" s="9"/>
     </row>
     <row r="24" spans="1:9" ht="65" customHeight="1">
       <c r="A24" s="5" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E24" s="7">
-        <v>0.75</v>
+        <v>0.79166666666666663</v>
       </c>
       <c r="F24" s="7">
-        <v>0.83333333333333337</v>
-      </c>
-      <c r="G24" s="8">
-        <v>0.75</v>
-      </c>
-      <c r="H24" s="8">
-        <v>0.83333333333333337</v>
-      </c>
-      <c r="I24" s="5" t="s">
-        <v>50</v>
-      </c>
+        <v>0.875</v>
+      </c>
+      <c r="G24" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="H24" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="I24" s="5"/>
     </row>
     <row r="25" spans="1:9" ht="65" customHeight="1">
       <c r="A25" s="5" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="C25" s="13">
+        <v>28</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E25" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F25" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G25" s="8">
         <v>0.66666666666666663</v>
       </c>
-      <c r="D25" s="13">
-        <v>0.91666666666666663</v>
-      </c>
-      <c r="E25" s="11">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="F25" s="11">
-        <v>0.91666666666666663</v>
-      </c>
-      <c r="G25" s="12">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="H25" s="12">
-        <v>0.91666666666666663</v>
-      </c>
-      <c r="I25" s="5" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" ht="31" customHeight="1">
-      <c r="A26" s="14" t="s">
-        <v>39</v>
-      </c>
-      <c r="B26" s="14"/>
-      <c r="C26" s="14"/>
-      <c r="D26" s="14"/>
-      <c r="E26" s="14"/>
-      <c r="F26" s="14"/>
-      <c r="G26" s="14"/>
-      <c r="H26" s="14"/>
-      <c r="I26" s="14"/>
-    </row>
-    <row r="27" spans="1:9" ht="65" customHeight="1">
-      <c r="A27" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="C27" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D27" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E27" s="7">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="F27" s="7">
-        <v>0.875</v>
-      </c>
-      <c r="G27" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="H27" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="I27" s="5" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" ht="65" customHeight="1">
-      <c r="A28" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="C28" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D28" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E28" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F28" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="G28" s="8">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="H28" s="8">
+      <c r="H25" s="8">
         <v>0.75</v>
       </c>
-      <c r="I28" s="5" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" ht="65" customHeight="1">
-      <c r="A29" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="C29" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D29" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E29" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F29" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="G29" s="9">
-        <v>0.95833333333333337</v>
-      </c>
-      <c r="H29" s="10">
-        <v>4.1666666666666664E-2</v>
-      </c>
-      <c r="I29" s="5" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" ht="26" customHeight="1">
-      <c r="A30" s="1"/>
-      <c r="B30" s="1"/>
-      <c r="C30" s="1"/>
-      <c r="D30" s="1"/>
-      <c r="E30" s="1"/>
-      <c r="F30" s="1"/>
-      <c r="G30" s="1"/>
-      <c r="H30" s="1"/>
-      <c r="I30" s="1"/>
-    </row>
-    <row r="31" spans="1:9" ht="25" customHeight="1">
-      <c r="A31" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B31" s="1"/>
-      <c r="C31" s="1"/>
-      <c r="D31" s="1"/>
-      <c r="E31" s="1"/>
-      <c r="F31" s="1"/>
-      <c r="G31" s="1"/>
-      <c r="H31" s="1"/>
-      <c r="I31" s="1"/>
+      <c r="I25" s="5"/>
+    </row>
+    <row r="26" spans="1:9" ht="26" customHeight="1">
+      <c r="A26" s="1"/>
+      <c r="B26" s="1"/>
+      <c r="C26" s="1"/>
+      <c r="D26" s="1"/>
+      <c r="E26" s="1"/>
+      <c r="F26" s="1"/>
+      <c r="G26" s="1"/>
+      <c r="H26" s="1"/>
+      <c r="I26" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="A6:I6"/>
     <mergeCell ref="A9:I9"/>
-    <mergeCell ref="A12:I12"/>
-    <mergeCell ref="A17:I17"/>
-    <mergeCell ref="A22:I22"/>
-    <mergeCell ref="A26:I26"/>
+    <mergeCell ref="A14:I14"/>
+    <mergeCell ref="A19:I19"/>
+    <mergeCell ref="A23:I23"/>
   </mergeCells>
-  <conditionalFormatting sqref="B10:B29">
+  <conditionalFormatting sqref="B7:B25">
     <cfRule type="containsText" dxfId="1" priority="2" operator="containsText" text="*"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C10:H29">
+  <conditionalFormatting sqref="C7:H25">
     <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="не задано"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="8" scale="88" fitToHeight="0" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>